--- a/data/trans_dic/P21D_4_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,86</t>
+          <t>0,29; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,72</t>
+          <t>0,11; 0,73</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,48</t>
+          <t>0,05; 1,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,81</t>
+          <t>0,68; 2,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,74</t>
+          <t>0,52; 1,76</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,52</t>
+          <t>0,05; 0,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,31</t>
+          <t>0,49; 1,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,76</t>
+          <t>0,31; 0,81</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3826</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2870</t>
+          <t>0; 2916</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4485</t>
+          <t>0; 4562</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1565; 8305</t>
+          <t>1282; 7365</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1030; 7906</t>
+          <t>1223; 8062</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6584</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164; 4853</t>
+          <t>167; 4276</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>749; 7408</t>
+          <t>746; 7361</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5920</t>
+          <t>0; 6076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3269; 14560</t>
+          <t>3502; 14425</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4396; 16139</t>
+          <t>4775; 16310</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>676; 8695</t>
+          <t>796; 9442</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8255; 20783</t>
+          <t>7828; 21203</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9917; 24816</t>
+          <t>10170; 26447</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_4_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,65</t>
+          <t>0,37; 1,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,73</t>
+          <t>0,2; 0,95</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,3</t>
+          <t>0,13; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,12</t>
+          <t>0,1; 0,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,79</t>
+          <t>0,75; 3,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,76</t>
+          <t>0,53; 1,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,57</t>
+          <t>0,07; 0,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,33</t>
+          <t>0,52; 1,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,81</t>
+          <t>0,36; 0,82</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>648</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1308</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4086</t>
+          <t>0; 4367</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2916</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4562</t>
+          <t>0; 4462</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4457</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1282; 7365</t>
+          <t>1873; 9114</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1223; 8062</t>
+          <t>1921; 9264</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2836</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>0; 5586</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>167; 4276</t>
+          <t>506; 5028</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>746; 7361</t>
+          <t>731; 7339</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9066</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6076</t>
+          <t>0; 5864</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3502; 14425</t>
+          <t>3670; 14878</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4775; 16310</t>
+          <t>4868; 17044</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>17667</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>796; 9442</t>
+          <t>1149; 8584</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7828; 21203</t>
+          <t>8822; 21994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10170; 26447</t>
+          <t>11739; 26607</t>
         </is>
       </c>
     </row>
